--- a/tools/importer/reports/import-patient-information.report.xlsx
+++ b/tools/importer/reports/import-patient-information.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,6 +37,30 @@
     <t>url</t>
   </si>
   <si>
+    <t>fragments/stroke-awareness-related-links.report.json</t>
+  </si>
+  <si>
+    <t>["columns-related-links"]</t>
+  </si>
+  <si>
+    <t>fragments/stroke-awareness-related-links</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>sa-related-links-fragment</t>
+  </si>
+  <si>
+    <t>2026-08-28T11:11:32.136Z</t>
+  </si>
+  <si>
+    <t>Stroke Awareness Related Links (fragment)</t>
+  </si>
+  <si>
+    <t>https://patients.stryker.com/ww/en/stroke-awareness/resources.html</t>
+  </si>
+  <si>
     <t>us/en/stroke-awareness/patient-information.report.json</t>
   </si>
   <si>
@@ -46,19 +70,34 @@
     <t>us/en/stroke-awareness/patient-information</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>patient-education</t>
   </si>
   <si>
-    <t>2026-09-01T11:53:35.865Z</t>
+    <t>2026-09-01T13:08:25.379Z</t>
   </si>
   <si>
     <t>Neurovascular Patient Information | Stryker</t>
   </si>
   <si>
     <t>https://patients.stryker.com/us/en/stroke-awareness/patient-information.html</t>
+  </si>
+  <si>
+    <t>ww/en/stroke-awareness/resources.report.json</t>
+  </si>
+  <si>
+    <t>["hero","panel","cards-brochure","cards-brochure","fragment"]</t>
+  </si>
+  <si>
+    <t>ww/en/stroke-awareness/resources</t>
+  </si>
+  <si>
+    <t>sa-resources</t>
+  </si>
+  <si>
+    <t>2026-08-28T11:11:23.677Z</t>
+  </si>
+  <si>
+    <t>Stroke Awareness Resources | Stryker</t>
   </si>
 </sst>
 </file>
@@ -447,13 +486,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="1" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="44" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="5" max="5" width="27" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="7" width="45" customWidth="1"/>
     <col min="8" max="8" width="50" customWidth="1"/>
@@ -511,6 +549,58 @@
         <v>15</v>
       </c>
     </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
